--- a/1-LATEX/2-DADOS/3-OUTPUT/leave_one_out.xlsx
+++ b/1-LATEX/2-DADOS/3-OUTPUT/leave_one_out.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E223"/>
+  <dimension ref="A1:E327"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="D39">
-        <v>0.04705083067449972</v>
+        <v>0.01320986892636758</v>
       </c>
       <c r="E39">
-        <v>0.02328168911756996</v>
+        <v>0.02720094162764244</v>
       </c>
     </row>
     <row r="40">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="D40">
-        <v>0.03396081780170178</v>
+        <v>-0.005226459988879104</v>
       </c>
       <c r="E40">
-        <v>0.02475557462892868</v>
+        <v>0.02521737933590053</v>
       </c>
     </row>
     <row r="41">
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="D41">
-        <v>0.05350841160289502</v>
+        <v>0.03761582328528525</v>
       </c>
       <c r="E41">
-        <v>0.02186524162284369</v>
+        <v>0.02101253049747247</v>
       </c>
     </row>
     <row r="42">
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="D42">
-        <v>0.02159704359676002</v>
+        <v>-0.003376423373563241</v>
       </c>
       <c r="E42">
-        <v>0.01806566827367829</v>
+        <v>0.02216362239162193</v>
       </c>
     </row>
     <row r="43">
@@ -1247,10 +1247,10 @@
         </is>
       </c>
       <c r="D43">
-        <v>0.059949392705567</v>
+        <v>0.004437683158964528</v>
       </c>
       <c r="E43">
-        <v>0.02142364482885156</v>
+        <v>0.0291039605907924</v>
       </c>
     </row>
     <row r="44">
@@ -1268,10 +1268,10 @@
         </is>
       </c>
       <c r="D44">
-        <v>0.04609757055577444</v>
+        <v>0.01787952203947207</v>
       </c>
       <c r="E44">
-        <v>0.02130376134537122</v>
+        <v>0.02388810773253648</v>
       </c>
     </row>
     <row r="45">
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="D45">
-        <v>0.04449658334473977</v>
+        <v>0.01597256985281222</v>
       </c>
       <c r="E45">
-        <v>0.02130985836021335</v>
+        <v>0.02404836983388259</v>
       </c>
     </row>
     <row r="46">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="D46">
-        <v>0.04449658334473977</v>
+        <v>0.01817305382595772</v>
       </c>
       <c r="E46">
-        <v>0.02130985836021335</v>
+        <v>0.02382139829564433</v>
       </c>
     </row>
     <row r="47">
@@ -1331,10 +1331,10 @@
         </is>
       </c>
       <c r="D47">
-        <v>0.04449658334473977</v>
+        <v>0.01817305382595772</v>
       </c>
       <c r="E47">
-        <v>0.02130985836021335</v>
+        <v>0.02382139829564433</v>
       </c>
     </row>
     <row r="48">
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="D48">
-        <v>0.04449658334473977</v>
+        <v>0.01817305382595772</v>
       </c>
       <c r="E48">
-        <v>0.02130985836021335</v>
+        <v>0.02382139829564433</v>
       </c>
     </row>
     <row r="49">
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="D49">
-        <v>0.04689222771647769</v>
+        <v>0.01876277948968814</v>
       </c>
       <c r="E49">
-        <v>0.02133706201785329</v>
+        <v>0.02385772951761831</v>
       </c>
     </row>
     <row r="50">
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="D50">
-        <v>0.04609757051142319</v>
+        <v>0.01787952190234549</v>
       </c>
       <c r="E50">
-        <v>0.02130376140611489</v>
+        <v>0.02388810779096224</v>
       </c>
     </row>
     <row r="51">
@@ -1415,10 +1415,10 @@
         </is>
       </c>
       <c r="D51">
-        <v>0.04425294904645544</v>
+        <v>0.01720950631775935</v>
       </c>
       <c r="E51">
-        <v>0.02136968074823895</v>
+        <v>0.02395988845239685</v>
       </c>
     </row>
     <row r="52">
@@ -1436,10 +1436,10 @@
         </is>
       </c>
       <c r="D52">
-        <v>0.04449658334473977</v>
+        <v>0.01817305384187459</v>
       </c>
       <c r="E52">
-        <v>0.02130985836021335</v>
+        <v>0.02382139828879365</v>
       </c>
     </row>
     <row r="53">
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="D53">
-        <v>0.04449658334473977</v>
+        <v>0.01817305384187459</v>
       </c>
       <c r="E53">
-        <v>0.02130985836021335</v>
+        <v>0.02382139828879365</v>
       </c>
     </row>
     <row r="54">
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="D54">
-        <v>0.04449658334473977</v>
+        <v>0.01817305384187459</v>
       </c>
       <c r="E54">
-        <v>0.02130985836021335</v>
+        <v>0.02382139828879365</v>
       </c>
     </row>
     <row r="55">
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="D55">
-        <v>0.04425294904645544</v>
+        <v>0.01559560284260417</v>
       </c>
       <c r="E55">
-        <v>0.02136968074823895</v>
+        <v>0.02414631967859049</v>
       </c>
     </row>
     <row r="56">
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="D56">
-        <v>0.04425294904645544</v>
+        <v>0.01559560284260417</v>
       </c>
       <c r="E56">
-        <v>0.02136968074823895</v>
+        <v>0.02414631967859049</v>
       </c>
     </row>
     <row r="57">
@@ -1541,10 +1541,10 @@
         </is>
       </c>
       <c r="D57">
-        <v>0.04428963531273669</v>
+        <v>0.01607691488524754</v>
       </c>
       <c r="E57">
-        <v>0.02128504869291254</v>
+        <v>0.02402706870347806</v>
       </c>
     </row>
     <row r="58">
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="D58">
-        <v>0.04449658334473977</v>
+        <v>0.01817305384187459</v>
       </c>
       <c r="E58">
-        <v>0.02130985836021335</v>
+        <v>0.02382139828879365</v>
       </c>
     </row>
     <row r="59">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="D59">
-        <v>0.04449658334473977</v>
+        <v>0.01817305384187459</v>
       </c>
       <c r="E59">
-        <v>0.02130985836021335</v>
+        <v>0.02382139828879365</v>
       </c>
     </row>
     <row r="60">
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="D60">
-        <v>0.07694312137232033</v>
+        <v>0.02319050417844737</v>
       </c>
       <c r="E60">
-        <v>0.01444852568213653</v>
+        <v>0.02412020074123042</v>
       </c>
     </row>
     <row r="61">
@@ -1625,10 +1625,10 @@
         </is>
       </c>
       <c r="D61">
-        <v>0.03137822966453419</v>
+        <v>-0.0003333286099594436</v>
       </c>
       <c r="E61">
-        <v>0.02321134072242745</v>
+        <v>0.0264275095861588</v>
       </c>
     </row>
     <row r="62">
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="D62">
-        <v>0.04428963530956588</v>
+        <v>0.01941982698842207</v>
       </c>
       <c r="E62">
-        <v>0.02128504869694818</v>
+        <v>0.02363889140669929</v>
       </c>
     </row>
     <row r="63">
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="D63">
-        <v>0.04390828328850734</v>
+        <v>0.01575403779456533</v>
       </c>
       <c r="E63">
-        <v>0.02132663575841576</v>
+        <v>0.02411300635506233</v>
       </c>
     </row>
     <row r="64">
@@ -1688,10 +1688,10 @@
         </is>
       </c>
       <c r="D64">
-        <v>0.06269834721414085</v>
+        <v>0.04442806986855607</v>
       </c>
       <c r="E64">
-        <v>0.01820856412034541</v>
+        <v>0.01740815600511747</v>
       </c>
     </row>
     <row r="65">
@@ -1709,10 +1709,10 @@
         </is>
       </c>
       <c r="D65">
-        <v>0.04488251824082515</v>
+        <v>0.0202474327992441</v>
       </c>
       <c r="E65">
-        <v>0.02124008304270433</v>
+        <v>0.02367460017379045</v>
       </c>
     </row>
     <row r="66">
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="D66">
-        <v>0.04699322503628777</v>
+        <v>0.01887635485024652</v>
       </c>
       <c r="E66">
-        <v>0.0213400460897081</v>
+        <v>0.02385251360127933</v>
       </c>
     </row>
     <row r="67">
@@ -1751,10 +1751,10 @@
         </is>
       </c>
       <c r="D67">
-        <v>0.0444837861415599</v>
+        <v>0.01822386915557872</v>
       </c>
       <c r="E67">
-        <v>0.02131302001441691</v>
+        <v>0.02381821020753389</v>
       </c>
     </row>
     <row r="68">
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="D68">
-        <v>0.04692939078344751</v>
+        <v>0.01256592331351694</v>
       </c>
       <c r="E68">
-        <v>0.02400918776371654</v>
+        <v>0.02761065353500276</v>
       </c>
     </row>
     <row r="69">
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="D69">
-        <v>0.03137822966453419</v>
+        <v>-0.0003339876682060762</v>
       </c>
       <c r="E69">
-        <v>0.02321134072242745</v>
+        <v>0.02864145438997306</v>
       </c>
     </row>
     <row r="70">
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="D70">
-        <v>0.02399772559879074</v>
+        <v>0.002051284153815041</v>
       </c>
       <c r="E70">
-        <v>0.01903777059367989</v>
+        <v>0.0206532993645525</v>
       </c>
     </row>
     <row r="71">
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="D71">
-        <v>0.04488251821671847</v>
+        <v>0.02027107625750406</v>
       </c>
       <c r="E71">
-        <v>0.02124008307408755</v>
+        <v>0.02367234895091389</v>
       </c>
     </row>
     <row r="72">
@@ -1856,10 +1856,10 @@
         </is>
       </c>
       <c r="D72">
-        <v>0.04390828330030599</v>
+        <v>0.02111657707487698</v>
       </c>
       <c r="E72">
-        <v>0.02132663574360071</v>
+        <v>0.02341367579091846</v>
       </c>
     </row>
     <row r="73">
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="D73">
-        <v>0.04451035603773847</v>
+        <v>0.0157062965886837</v>
       </c>
       <c r="E73">
-        <v>0.02130645330041565</v>
+        <v>0.02411437309041435</v>
       </c>
     </row>
     <row r="74">
@@ -1893,10 +1893,10 @@
         <v>37</v>
       </c>
       <c r="D74">
-        <v>0.04689222772886489</v>
+        <v>0.01876277950784316</v>
       </c>
       <c r="E74">
-        <v>0.02133706200036524</v>
+        <v>0.02385772951266022</v>
       </c>
     </row>
     <row r="75">
@@ -1909,10 +1909,10 @@
         <v>39</v>
       </c>
       <c r="D75">
-        <v>0.04609757056864436</v>
+        <v>0.01787952176959581</v>
       </c>
       <c r="E75">
-        <v>0.02130376132774452</v>
+        <v>0.02388810785721837</v>
       </c>
     </row>
     <row r="76">
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="D76">
-        <v>0.03034226318028965</v>
+        <v>-0.009565383592858145</v>
       </c>
       <c r="E76">
-        <v>0.02998033511594072</v>
+        <v>0.1051319326262171</v>
       </c>
     </row>
     <row r="77">
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="D77">
-        <v>0.0379902012478894</v>
+        <v>0.001890989798959731</v>
       </c>
       <c r="E77">
-        <v>0.03633112191982193</v>
+        <v>0.1065376955099885</v>
       </c>
     </row>
     <row r="78">
@@ -1972,10 +1972,10 @@
         </is>
       </c>
       <c r="D78">
-        <v>0.07457295640656277</v>
+        <v>0.00564666746991359</v>
       </c>
       <c r="E78">
-        <v>0.02765223619707955</v>
+        <v>0.09388584982240933</v>
       </c>
     </row>
     <row r="79">
@@ -1993,10 +1993,10 @@
         </is>
       </c>
       <c r="D79">
-        <v>0.07023539921755964</v>
+        <v>0.01100486819297191</v>
       </c>
       <c r="E79">
-        <v>0.02819476763695067</v>
+        <v>0.09466727690502132</v>
       </c>
     </row>
     <row r="80">
@@ -2014,10 +2014,10 @@
         </is>
       </c>
       <c r="D80">
-        <v>0.07457295640656277</v>
+        <v>0.01100486819297191</v>
       </c>
       <c r="E80">
-        <v>0.02765223619707955</v>
+        <v>0.09466727690502132</v>
       </c>
     </row>
     <row r="81">
@@ -2035,10 +2035,10 @@
         </is>
       </c>
       <c r="D81">
-        <v>0.07457295640656277</v>
+        <v>0.004592969501674647</v>
       </c>
       <c r="E81">
-        <v>0.02765223619707955</v>
+        <v>0.09462213462708009</v>
       </c>
     </row>
     <row r="82">
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="D82">
-        <v>0.07457295640656277</v>
+        <v>0.01100486819297191</v>
       </c>
       <c r="E82">
-        <v>0.02765223619707955</v>
+        <v>0.09466727690502132</v>
       </c>
     </row>
     <row r="83">
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="D83">
-        <v>0.07667552126073479</v>
+        <v>0.004592969501674647</v>
       </c>
       <c r="E83">
-        <v>0.02749719291273609</v>
+        <v>0.09462213462708009</v>
       </c>
     </row>
     <row r="84">
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="D84">
-        <v>0.07457295640656277</v>
+        <v>0.01100486819297191</v>
       </c>
       <c r="E84">
-        <v>0.02765223619707955</v>
+        <v>0.09466727690502132</v>
       </c>
     </row>
     <row r="85">
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="D85">
-        <v>0.07457295640656277</v>
+        <v>0.01100486819297191</v>
       </c>
       <c r="E85">
-        <v>0.02765223619707955</v>
+        <v>0.09466727690502132</v>
       </c>
     </row>
     <row r="86">
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="D86">
-        <v>0.07457295640656277</v>
+        <v>0.01100486819297191</v>
       </c>
       <c r="E86">
-        <v>0.02765223619707955</v>
+        <v>0.09466727690502132</v>
       </c>
     </row>
     <row r="87">
@@ -2161,10 +2161,10 @@
         </is>
       </c>
       <c r="D87">
-        <v>0.07457295640656277</v>
+        <v>0.00564666746991359</v>
       </c>
       <c r="E87">
-        <v>0.02765223619707955</v>
+        <v>0.09388584982240933</v>
       </c>
     </row>
     <row r="88">
@@ -2182,10 +2182,10 @@
         </is>
       </c>
       <c r="D88">
-        <v>0.07457295640656277</v>
+        <v>0.01100486819297192</v>
       </c>
       <c r="E88">
-        <v>0.02765223619707955</v>
+        <v>0.09466727690502132</v>
       </c>
     </row>
     <row r="89">
@@ -2203,10 +2203,10 @@
         </is>
       </c>
       <c r="D89">
-        <v>0.06936790189147397</v>
+        <v>0.007339089835062433</v>
       </c>
       <c r="E89">
-        <v>0.02853981012510627</v>
+        <v>0.09300285755201508</v>
       </c>
     </row>
     <row r="90">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="D90">
-        <v>0.06936790189147397</v>
+        <v>0.004592969501674647</v>
       </c>
       <c r="E90">
-        <v>0.02853981012510627</v>
+        <v>0.09462213462708009</v>
       </c>
     </row>
     <row r="91">
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="D91">
-        <v>0.07023539920101328</v>
+        <v>0.005646667470873768</v>
       </c>
       <c r="E91">
-        <v>0.02819476764768528</v>
+        <v>0.09388584981815078</v>
       </c>
     </row>
     <row r="92">
@@ -2266,10 +2266,10 @@
         </is>
       </c>
       <c r="D92">
-        <v>0.07457295640656277</v>
+        <v>0.007365839124170956</v>
       </c>
       <c r="E92">
-        <v>0.02765223619707955</v>
+        <v>0.09284466614397953</v>
       </c>
     </row>
     <row r="93">
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="D93">
-        <v>0.07457295640656277</v>
+        <v>0.00564666746991359</v>
       </c>
       <c r="E93">
-        <v>0.02765223619707955</v>
+        <v>0.09388584982240933</v>
       </c>
     </row>
     <row r="94">
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="D94">
-        <v>0.06999887835079215</v>
+        <v>0.01295821063175712</v>
       </c>
       <c r="E94">
-        <v>0.031414534295862</v>
+        <v>0.09555219277712404</v>
       </c>
     </row>
     <row r="95">
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="D95">
-        <v>0.06997155383264131</v>
+        <v>0.05818029691701984</v>
       </c>
       <c r="E95">
-        <v>0.0315103988218574</v>
+        <v>0.07264501879119459</v>
       </c>
     </row>
     <row r="96">
@@ -2350,10 +2350,10 @@
         </is>
       </c>
       <c r="D96">
-        <v>0.04347799464571377</v>
+        <v>-0.02460305140373478</v>
       </c>
       <c r="E96">
-        <v>0.02965504868471198</v>
+        <v>0.09150998484705257</v>
       </c>
     </row>
     <row r="97">
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="D97">
-        <v>0.07457295636162668</v>
+        <v>0.00564666746991359</v>
       </c>
       <c r="E97">
-        <v>0.02765223622634146</v>
+        <v>0.09388584982240933</v>
       </c>
     </row>
     <row r="98">
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="D98">
-        <v>0.06936790187260687</v>
+        <v>0.004592969501674647</v>
       </c>
       <c r="E98">
-        <v>0.02853981013742529</v>
+        <v>0.09462213462708009</v>
       </c>
     </row>
     <row r="99">
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="D99">
-        <v>0.07457295636162668</v>
+        <v>0.007365839135383981</v>
       </c>
       <c r="E99">
-        <v>0.02765223622634146</v>
+        <v>0.09284466609297973</v>
       </c>
     </row>
     <row r="100">
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="D100">
-        <v>0.07664382241817369</v>
+        <v>0.007339089834267119</v>
       </c>
       <c r="E100">
-        <v>0.02750028938190976</v>
+        <v>0.09300285755563707</v>
       </c>
     </row>
     <row r="101">
@@ -2455,10 +2455,10 @@
         </is>
       </c>
       <c r="D101">
-        <v>0.15999198829456</v>
+        <v>0.01100486819931663</v>
       </c>
       <c r="E101">
-        <v>0.006098175269548698</v>
+        <v>0.09466727687358689</v>
       </c>
     </row>
     <row r="102">
@@ -2476,10 +2476,10 @@
         </is>
       </c>
       <c r="D102">
-        <v>0.0769520153945385</v>
+        <v>0.08401455953239165</v>
       </c>
       <c r="E102">
-        <v>0.0274692740905122</v>
+        <v>0.04528282287377813</v>
       </c>
     </row>
     <row r="103">
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="D103">
-        <v>0.07468064836685255</v>
+        <v>0.005589489113137244</v>
       </c>
       <c r="E103">
-        <v>0.02764694955658541</v>
+        <v>0.09392642803132485</v>
       </c>
     </row>
     <row r="104">
@@ -2518,10 +2518,10 @@
         </is>
       </c>
       <c r="D104">
-        <v>0.06999887831763671</v>
+        <v>0.005661866968659808</v>
       </c>
       <c r="E104">
-        <v>0.03141453431887495</v>
+        <v>0.1031084505869408</v>
       </c>
     </row>
     <row r="105">
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="D105">
-        <v>0.06999887831763671</v>
+        <v>-0.02460305141185069</v>
       </c>
       <c r="E105">
-        <v>0.03141453431887495</v>
+        <v>0.09150998488911063</v>
       </c>
     </row>
     <row r="106">
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="D106">
-        <v>0.04273679603416543</v>
+        <v>-0.0413737910106878</v>
       </c>
       <c r="E106">
-        <v>0.02077042286818328</v>
+        <v>0.06748223880430815</v>
       </c>
     </row>
     <row r="107">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="D107">
-        <v>0.07667552128626755</v>
+        <v>0.01295821065144878</v>
       </c>
       <c r="E107">
-        <v>0.02749719289611184</v>
+        <v>0.09555219267771146</v>
       </c>
     </row>
     <row r="108">
@@ -2602,10 +2602,10 @@
         </is>
       </c>
       <c r="D108">
-        <v>0.06936790185599269</v>
+        <v>0.004592969513253106</v>
       </c>
       <c r="E108">
-        <v>0.02853981014827328</v>
+        <v>0.09462213457619854</v>
       </c>
     </row>
     <row r="109">
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="D109">
-        <v>0.07667552128626755</v>
+        <v>0.007339089826930843</v>
       </c>
       <c r="E109">
-        <v>0.02749719289611184</v>
+        <v>0.09300285758904624</v>
       </c>
     </row>
     <row r="110">
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="D110">
-        <v>0.06944786302146734</v>
+        <v>0.005708436662391439</v>
       </c>
       <c r="E110">
-        <v>0.02850802556327561</v>
+        <v>0.09384193503583657</v>
       </c>
     </row>
     <row r="111">
@@ -2660,10 +2660,10 @@
         <v>37</v>
       </c>
       <c r="D111">
-        <v>0.07667552128626755</v>
+        <v>0.01295821065144878</v>
       </c>
       <c r="E111">
-        <v>0.02749719289611184</v>
+        <v>0.09555219267771146</v>
       </c>
     </row>
     <row r="112">
@@ -2676,10 +2676,10 @@
         <v>39</v>
       </c>
       <c r="D112">
-        <v>0.07457295635753758</v>
+        <v>0.005646667473234183</v>
       </c>
       <c r="E112">
-        <v>0.02765223622900418</v>
+        <v>0.09388584980768182</v>
       </c>
     </row>
     <row r="113">
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="D113">
-        <v>-0.009565383592858145</v>
+        <v>-0.3539204122599889</v>
       </c>
       <c r="E113">
-        <v>0.1051319326262171</v>
+        <v>0.09715937801989</v>
       </c>
     </row>
     <row r="114">
@@ -2710,18 +2710,18 @@
         </is>
       </c>
       <c r="B114">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Rodríguez-Cruz, L.A.; Álvarez-Berríos, N.; Niles, M.T.</t>
+          <t>Frascaroli, F; Bhagwat, S; Guarino, R; Chiarucci,</t>
         </is>
       </c>
       <c r="D114">
-        <v>0.001890989798959731</v>
+        <v>-0.3268623748614588</v>
       </c>
       <c r="E114">
-        <v>0.1065376955099885</v>
+        <v>0.1392058025196724</v>
       </c>
     </row>
     <row r="115">
@@ -2731,18 +2731,18 @@
         </is>
       </c>
       <c r="B115">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Calvet-Mir L.</t>
+          <t>Rodríguez-Cruz, L.A.; Álvarez-Berríos, N.; Niles, M.T.</t>
         </is>
       </c>
       <c r="D115">
-        <v>0.00564666746991359</v>
+        <v>-0.277933080080803</v>
       </c>
       <c r="E115">
-        <v>0.09388584982240933</v>
+        <v>0.1817005576700135</v>
       </c>
     </row>
     <row r="116">
@@ -2752,18 +2752,18 @@
         </is>
       </c>
       <c r="B116">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bastos J.G.</t>
+          <t>Calvet-Mir L.</t>
         </is>
       </c>
       <c r="D116">
-        <v>0.01100486819297191</v>
+        <v>-0.2796574726268213</v>
       </c>
       <c r="E116">
-        <v>0.09466727690502132</v>
+        <v>0.173859301811775</v>
       </c>
     </row>
     <row r="117">
@@ -2773,18 +2773,18 @@
         </is>
       </c>
       <c r="B117">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Romero-Silva M.J.</t>
+          <t>Bastos J.G.</t>
         </is>
       </c>
       <c r="D117">
-        <v>0.01100486819297191</v>
+        <v>-0.280063649516334</v>
       </c>
       <c r="E117">
-        <v>0.09466727690502132</v>
+        <v>0.1752485703764899</v>
       </c>
     </row>
     <row r="118">
@@ -2794,18 +2794,18 @@
         </is>
       </c>
       <c r="B118">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>de Sousa T.B.</t>
+          <t>Romero-Silva M.J.</t>
         </is>
       </c>
       <c r="D118">
-        <v>0.004592969501674647</v>
+        <v>-0.280063649516334</v>
       </c>
       <c r="E118">
-        <v>0.09462213462708009</v>
+        <v>0.1752485703764899</v>
       </c>
     </row>
     <row r="119">
@@ -2815,18 +2815,18 @@
         </is>
       </c>
       <c r="B119">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Sarmiento F.O.</t>
+          <t>de Sousa T.B.</t>
         </is>
       </c>
       <c r="D119">
-        <v>0.01100486819297191</v>
+        <v>-0.280063649516334</v>
       </c>
       <c r="E119">
-        <v>0.09466727690502132</v>
+        <v>0.1752485703764899</v>
       </c>
     </row>
     <row r="120">
@@ -2836,18 +2836,18 @@
         </is>
       </c>
       <c r="B120">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Aldasoro Maya E.M.</t>
+          <t>Sarmiento F.O.</t>
         </is>
       </c>
       <c r="D120">
-        <v>0.004592969501674647</v>
+        <v>-0.280063649516334</v>
       </c>
       <c r="E120">
-        <v>0.09462213462708009</v>
+        <v>0.1752485703764899</v>
       </c>
     </row>
     <row r="121">
@@ -2857,18 +2857,18 @@
         </is>
       </c>
       <c r="B121">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Franco-Moraes J.</t>
+          <t>Aldasoro Maya E.M.</t>
         </is>
       </c>
       <c r="D121">
-        <v>0.01100486819297191</v>
+        <v>-0.280063649516334</v>
       </c>
       <c r="E121">
-        <v>0.09466727690502132</v>
+        <v>0.1752485703764899</v>
       </c>
     </row>
     <row r="122">
@@ -2878,18 +2878,18 @@
         </is>
       </c>
       <c r="B122">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Latorre E.C.</t>
+          <t>Franco-Moraes J.</t>
         </is>
       </c>
       <c r="D122">
-        <v>0.01100486819297191</v>
+        <v>-0.280063649516334</v>
       </c>
       <c r="E122">
-        <v>0.09466727690502132</v>
+        <v>0.1752485703764899</v>
       </c>
     </row>
     <row r="123">
@@ -2899,18 +2899,18 @@
         </is>
       </c>
       <c r="B123">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Mobarak C.</t>
+          <t>Latorre E.C.</t>
         </is>
       </c>
       <c r="D123">
-        <v>0.01100486819297191</v>
+        <v>-0.280063649516334</v>
       </c>
       <c r="E123">
-        <v>0.09466727690502132</v>
+        <v>0.1752485703764899</v>
       </c>
     </row>
     <row r="124">
@@ -2920,18 +2920,18 @@
         </is>
       </c>
       <c r="B124">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Andreotti F.</t>
+          <t>Mobarak C.</t>
         </is>
       </c>
       <c r="D124">
-        <v>0.00564666746991359</v>
+        <v>-0.2796574726268213</v>
       </c>
       <c r="E124">
-        <v>0.09388584982240933</v>
+        <v>0.173859301811775</v>
       </c>
     </row>
     <row r="125">
@@ -2941,18 +2941,18 @@
         </is>
       </c>
       <c r="B125">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Suwardi A.B.</t>
+          <t>Andreotti F.</t>
         </is>
       </c>
       <c r="D125">
-        <v>0.01100486819297192</v>
+        <v>-0.280063649516334</v>
       </c>
       <c r="E125">
-        <v>0.09466727690502132</v>
+        <v>0.1752485703764899</v>
       </c>
     </row>
     <row r="126">
@@ -2962,18 +2962,18 @@
         </is>
       </c>
       <c r="B126">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Plieninger T.</t>
+          <t>Suwardi A.B.</t>
         </is>
       </c>
       <c r="D126">
-        <v>0.007339089835062433</v>
+        <v>-0.2636857030477106</v>
       </c>
       <c r="E126">
-        <v>0.09300285755201508</v>
+        <v>0.173805175695575</v>
       </c>
     </row>
     <row r="127">
@@ -2983,18 +2983,18 @@
         </is>
       </c>
       <c r="B127">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Oloriz C.</t>
+          <t>Plieninger T.</t>
         </is>
       </c>
       <c r="D127">
-        <v>0.004592969501674647</v>
+        <v>-0.2795270447513896</v>
       </c>
       <c r="E127">
-        <v>0.09462213462708009</v>
+        <v>0.1711747403183831</v>
       </c>
     </row>
     <row r="128">
@@ -3004,18 +3004,18 @@
         </is>
       </c>
       <c r="B128">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Tran T.A.</t>
+          <t>Oloriz C.</t>
         </is>
       </c>
       <c r="D128">
-        <v>0.005646667470873768</v>
+        <v>-0.284694644713427</v>
       </c>
       <c r="E128">
-        <v>0.09388584981815078</v>
+        <v>0.1725819904530238</v>
       </c>
     </row>
     <row r="129">
@@ -3025,18 +3025,18 @@
         </is>
       </c>
       <c r="B129">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Saiba Y.</t>
+          <t>Tran T.A.</t>
         </is>
       </c>
       <c r="D129">
-        <v>0.007365839124170956</v>
+        <v>-0.2800636495170832</v>
       </c>
       <c r="E129">
-        <v>0.09284466614397953</v>
+        <v>0.1752485705229925</v>
       </c>
     </row>
     <row r="130">
@@ -3046,18 +3046,18 @@
         </is>
       </c>
       <c r="B130">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Vázquez-Delfin P.</t>
+          <t>Saiba Y.</t>
         </is>
       </c>
       <c r="D130">
-        <v>0.00564666746991359</v>
+        <v>-0.2796574726268213</v>
       </c>
       <c r="E130">
-        <v>0.09388584982240933</v>
+        <v>0.173859301811775</v>
       </c>
     </row>
     <row r="131">
@@ -3067,18 +3067,18 @@
         </is>
       </c>
       <c r="B131">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Nord A.</t>
+          <t>Vázquez-Delfin P.</t>
         </is>
       </c>
       <c r="D131">
-        <v>0.01295821063175712</v>
+        <v>-0.2796574726268213</v>
       </c>
       <c r="E131">
-        <v>0.09555219277712404</v>
+        <v>0.173859301811775</v>
       </c>
     </row>
     <row r="132">
@@ -3088,18 +3088,18 @@
         </is>
       </c>
       <c r="B132">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Tabe-Ojong M.P.</t>
+          <t>Nord A.</t>
         </is>
       </c>
       <c r="D132">
-        <v>0.05818029691701984</v>
+        <v>-0.2489197989811381</v>
       </c>
       <c r="E132">
-        <v>0.07264501879119459</v>
+        <v>0.1637262055920253</v>
       </c>
     </row>
     <row r="133">
@@ -3109,18 +3109,18 @@
         </is>
       </c>
       <c r="B133">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Aniah P.</t>
+          <t>Tabe-Ojong M.P.</t>
         </is>
       </c>
       <c r="D133">
-        <v>-0.02460305140373478</v>
+        <v>-0.2554241833556015</v>
       </c>
       <c r="E133">
-        <v>0.09150998484705257</v>
+        <v>0.1682287265826847</v>
       </c>
     </row>
     <row r="134">
@@ -3130,18 +3130,18 @@
         </is>
       </c>
       <c r="B134">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Alemayehu A.</t>
+          <t>Aniah P.</t>
         </is>
       </c>
       <c r="D134">
-        <v>0.00564666746991359</v>
+        <v>-0.3146985426998847</v>
       </c>
       <c r="E134">
-        <v>0.09388584982240933</v>
+        <v>0.1555800567373109</v>
       </c>
     </row>
     <row r="135">
@@ -3151,18 +3151,18 @@
         </is>
       </c>
       <c r="B135">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>La Rosa A.</t>
+          <t>Alemayehu A.</t>
         </is>
       </c>
       <c r="D135">
-        <v>0.004592969501674647</v>
+        <v>-0.279657472626776</v>
       </c>
       <c r="E135">
-        <v>0.09462213462708009</v>
+        <v>0.1738593018044478</v>
       </c>
     </row>
     <row r="136">
@@ -3172,18 +3172,18 @@
         </is>
       </c>
       <c r="B136">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Fernández-Llamazares, A; Cabeza, M</t>
+          <t>La Rosa A.</t>
         </is>
       </c>
       <c r="D136">
-        <v>0.007365839135383981</v>
+        <v>-0.2800636495175829</v>
       </c>
       <c r="E136">
-        <v>0.09284466609297973</v>
+        <v>0.1752485706206822</v>
       </c>
     </row>
     <row r="137">
@@ -3193,18 +3193,18 @@
         </is>
       </c>
       <c r="B137">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Gerner, IR; Zerbe, S; Säumel, I</t>
+          <t>Fernández-Llamazares, A; Cabeza, M</t>
         </is>
       </c>
       <c r="D137">
-        <v>0.007339089834267119</v>
+        <v>-0.279657472626776</v>
       </c>
       <c r="E137">
-        <v>0.09300285755563707</v>
+        <v>0.1738593018044478</v>
       </c>
     </row>
     <row r="138">
@@ -3214,18 +3214,18 @@
         </is>
       </c>
       <c r="B138">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Frascaroli, F; Bhagwat, S; Guarino, R; Chiarucci,</t>
+          <t>Gerner, IR; Zerbe, S; Säumel, I</t>
         </is>
       </c>
       <c r="D138">
-        <v>0.01100486819931663</v>
+        <v>-0.2800584612928165</v>
       </c>
       <c r="E138">
-        <v>0.09466727687358689</v>
+        <v>0.1752309632185139</v>
       </c>
     </row>
     <row r="139">
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="D139">
-        <v>0.08401455953239165</v>
+        <v>-0.2801078992922455</v>
       </c>
       <c r="E139">
-        <v>0.04528282287377813</v>
+        <v>0.1753985931109907</v>
       </c>
     </row>
     <row r="140">
@@ -3264,10 +3264,10 @@
         </is>
       </c>
       <c r="D140">
-        <v>0.005589489113137244</v>
+        <v>-0.2616084161051431</v>
       </c>
       <c r="E140">
-        <v>0.09392642803132485</v>
+        <v>0.1759605504000444</v>
       </c>
     </row>
     <row r="141">
@@ -3285,10 +3285,10 @@
         </is>
       </c>
       <c r="D141">
-        <v>0.005661866968659808</v>
+        <v>-0.2636857030485499</v>
       </c>
       <c r="E141">
-        <v>0.1031084505869408</v>
+        <v>0.1738051757834869</v>
       </c>
     </row>
     <row r="142">
@@ -3306,10 +3306,10 @@
         </is>
       </c>
       <c r="D142">
-        <v>-0.02460305141185069</v>
+        <v>-0.2636857030485499</v>
       </c>
       <c r="E142">
-        <v>0.09150998488911063</v>
+        <v>0.1738051757834869</v>
       </c>
     </row>
     <row r="143">
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="D143">
-        <v>-0.0413737910106878</v>
+        <v>-0.2463422007738622</v>
       </c>
       <c r="E143">
-        <v>0.06748223880430815</v>
+        <v>0.1595078824472851</v>
       </c>
     </row>
     <row r="144">
@@ -3348,10 +3348,10 @@
         </is>
       </c>
       <c r="D144">
-        <v>0.01295821065144878</v>
+        <v>-0.2489197989812178</v>
       </c>
       <c r="E144">
-        <v>0.09555219267771146</v>
+        <v>0.1637262055937909</v>
       </c>
     </row>
     <row r="145">
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="D145">
-        <v>0.004592969513253106</v>
+        <v>-0.2800636495164435</v>
       </c>
       <c r="E145">
-        <v>0.09462213457619854</v>
+        <v>0.175248570397873</v>
       </c>
     </row>
     <row r="146">
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="D146">
-        <v>0.007339089826930843</v>
+        <v>-0.2800636495164435</v>
       </c>
       <c r="E146">
-        <v>0.09300285758904624</v>
+        <v>0.175248570397873</v>
       </c>
     </row>
     <row r="147">
@@ -3411,10 +3411,10 @@
         </is>
       </c>
       <c r="D147">
-        <v>0.005708436662391439</v>
+        <v>-0.2796307887700967</v>
       </c>
       <c r="E147">
-        <v>0.09384193503583657</v>
+        <v>0.173767279162987</v>
       </c>
     </row>
     <row r="148">
@@ -3427,10 +3427,10 @@
         <v>37</v>
       </c>
       <c r="D148">
-        <v>0.01295821065144878</v>
+        <v>-0.2800636495164435</v>
       </c>
       <c r="E148">
-        <v>0.09555219267771146</v>
+        <v>0.175248570397873</v>
       </c>
     </row>
     <row r="149">
@@ -3443,10 +3443,10 @@
         <v>39</v>
       </c>
       <c r="D149">
-        <v>0.005646667473234183</v>
+        <v>-0.2796574726261621</v>
       </c>
       <c r="E149">
-        <v>0.09388584980768182</v>
+        <v>0.1738593017045983</v>
       </c>
     </row>
     <row r="150">
@@ -3464,10 +3464,10 @@
         </is>
       </c>
       <c r="D150">
-        <v>-0.3539204122599889</v>
+        <v>0.1805237721631213</v>
       </c>
       <c r="E150">
-        <v>0.09715937801989</v>
+        <v>0.1172603097030837</v>
       </c>
     </row>
     <row r="151">
@@ -3485,10 +3485,10 @@
         </is>
       </c>
       <c r="D151">
-        <v>-0.3268623748614588</v>
+        <v>0.1098987150981599</v>
       </c>
       <c r="E151">
-        <v>0.1392058025196724</v>
+        <v>0.05895552165088383</v>
       </c>
     </row>
     <row r="152">
@@ -3506,10 +3506,10 @@
         </is>
       </c>
       <c r="D152">
-        <v>-0.277933080080803</v>
+        <v>0.1587417288265827</v>
       </c>
       <c r="E152">
-        <v>0.1817005576700135</v>
+        <v>0.1152312670517498</v>
       </c>
     </row>
     <row r="153">
@@ -3527,10 +3527,10 @@
         </is>
       </c>
       <c r="D153">
-        <v>-0.2796574726268213</v>
+        <v>0.1719167514163476</v>
       </c>
       <c r="E153">
-        <v>0.173859301811775</v>
+        <v>0.101455331262684</v>
       </c>
     </row>
     <row r="154">
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="D154">
-        <v>-0.280063649516334</v>
+        <v>0.1715541873910563</v>
       </c>
       <c r="E154">
-        <v>0.1752485703764899</v>
+        <v>0.1026687219327556</v>
       </c>
     </row>
     <row r="155">
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="D155">
-        <v>-0.280063649516334</v>
+        <v>0.1715541873910563</v>
       </c>
       <c r="E155">
-        <v>0.1752485703764899</v>
+        <v>0.1026687219327556</v>
       </c>
     </row>
     <row r="156">
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="D156">
-        <v>-0.280063649516334</v>
+        <v>0.1715541873910563</v>
       </c>
       <c r="E156">
-        <v>0.1752485703764899</v>
+        <v>0.1026687219327556</v>
       </c>
     </row>
     <row r="157">
@@ -3611,10 +3611,10 @@
         </is>
       </c>
       <c r="D157">
-        <v>-0.280063649516334</v>
+        <v>0.1715541873910563</v>
       </c>
       <c r="E157">
-        <v>0.1752485703764899</v>
+        <v>0.1026687219327556</v>
       </c>
     </row>
     <row r="158">
@@ -3632,10 +3632,10 @@
         </is>
       </c>
       <c r="D158">
-        <v>-0.280063649516334</v>
+        <v>0.1829001275211319</v>
       </c>
       <c r="E158">
-        <v>0.1752485703764899</v>
+        <v>0.1042322967106526</v>
       </c>
     </row>
     <row r="159">
@@ -3653,10 +3653,10 @@
         </is>
       </c>
       <c r="D159">
-        <v>-0.280063649516334</v>
+        <v>0.1790544092277229</v>
       </c>
       <c r="E159">
-        <v>0.1752485703764899</v>
+        <v>0.1036031146280961</v>
       </c>
     </row>
     <row r="160">
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="D160">
-        <v>-0.280063649516334</v>
+        <v>0.1715541874001326</v>
       </c>
       <c r="E160">
-        <v>0.1752485703764899</v>
+        <v>0.102668722213511</v>
       </c>
     </row>
     <row r="161">
@@ -3695,10 +3695,10 @@
         </is>
       </c>
       <c r="D161">
-        <v>-0.2796574726268213</v>
+        <v>0.1715541874001326</v>
       </c>
       <c r="E161">
-        <v>0.173859301811775</v>
+        <v>0.102668722213511</v>
       </c>
     </row>
     <row r="162">
@@ -3716,10 +3716,10 @@
         </is>
       </c>
       <c r="D162">
-        <v>-0.280063649516334</v>
+        <v>0.1790544092292201</v>
       </c>
       <c r="E162">
-        <v>0.1752485703764899</v>
+        <v>0.1036031146519171</v>
       </c>
     </row>
     <row r="163">
@@ -3737,10 +3737,10 @@
         </is>
       </c>
       <c r="D163">
-        <v>-0.2636857030477106</v>
+        <v>0.1715541874001326</v>
       </c>
       <c r="E163">
-        <v>0.173805175695575</v>
+        <v>0.102668722213511</v>
       </c>
     </row>
     <row r="164">
@@ -3758,10 +3758,10 @@
         </is>
       </c>
       <c r="D164">
-        <v>-0.2795270447513896</v>
+        <v>0.1715257293299964</v>
       </c>
       <c r="E164">
-        <v>0.1711747403183831</v>
+        <v>0.1035656042144892</v>
       </c>
     </row>
     <row r="165">
@@ -3779,10 +3779,10 @@
         </is>
       </c>
       <c r="D165">
-        <v>-0.284694644713427</v>
+        <v>0.1691049657960305</v>
       </c>
       <c r="E165">
-        <v>0.1725819904530238</v>
+        <v>0.1024697640444356</v>
       </c>
     </row>
     <row r="166">
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="D166">
-        <v>-0.2800636495170832</v>
+        <v>0.1700685989500717</v>
       </c>
       <c r="E166">
-        <v>0.1752485705229925</v>
+        <v>0.1019839276363107</v>
       </c>
     </row>
     <row r="167">
@@ -3821,10 +3821,10 @@
         </is>
       </c>
       <c r="D167">
-        <v>-0.2796574726268213</v>
+        <v>0.171554187394143</v>
       </c>
       <c r="E167">
-        <v>0.173859301811775</v>
+        <v>0.1026687220282354</v>
       </c>
     </row>
     <row r="168">
@@ -3842,10 +3842,10 @@
         </is>
       </c>
       <c r="D168">
-        <v>-0.2796574726268213</v>
+        <v>0.1700685989500717</v>
       </c>
       <c r="E168">
-        <v>0.173859301811775</v>
+        <v>0.1019839276363107</v>
       </c>
     </row>
     <row r="169">
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="D169">
-        <v>-0.2489197989811381</v>
+        <v>0.1829001275303344</v>
       </c>
       <c r="E169">
-        <v>0.1637262055920253</v>
+        <v>0.1042322968436479</v>
       </c>
     </row>
     <row r="170">
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="D170">
-        <v>-0.2554241833556015</v>
+        <v>0.2292775645298313</v>
       </c>
       <c r="E170">
-        <v>0.1682287265826847</v>
+        <v>0.06667755147540262</v>
       </c>
     </row>
     <row r="171">
@@ -3905,10 +3905,10 @@
         </is>
       </c>
       <c r="D171">
-        <v>-0.3146985426998847</v>
+        <v>0.1576896809062693</v>
       </c>
       <c r="E171">
-        <v>0.1555800567373109</v>
+        <v>0.1120948106396098</v>
       </c>
     </row>
     <row r="172">
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="D172">
-        <v>-0.279657472626776</v>
+        <v>0.1715541873930755</v>
       </c>
       <c r="E172">
-        <v>0.1738593018044478</v>
+        <v>0.102668721995211</v>
       </c>
     </row>
     <row r="173">
@@ -3947,10 +3947,10 @@
         </is>
       </c>
       <c r="D173">
-        <v>-0.2800636495175829</v>
+        <v>0.1715257293300479</v>
       </c>
       <c r="E173">
-        <v>0.1752485706206822</v>
+        <v>0.1035656042161268</v>
       </c>
     </row>
     <row r="174">
@@ -3968,10 +3968,10 @@
         </is>
       </c>
       <c r="D174">
-        <v>-0.279657472626776</v>
+        <v>0.1790544092292201</v>
       </c>
       <c r="E174">
-        <v>0.1738593018044478</v>
+        <v>0.1036031146519171</v>
       </c>
     </row>
     <row r="175">
@@ -3989,10 +3989,10 @@
         </is>
       </c>
       <c r="D175">
-        <v>-0.2800584612928165</v>
+        <v>0.1721244752054119</v>
       </c>
       <c r="E175">
-        <v>0.1752309632185139</v>
+        <v>0.1016531798131691</v>
       </c>
     </row>
     <row r="176">
@@ -4010,10 +4010,10 @@
         </is>
       </c>
       <c r="D176">
-        <v>-0.2801078992922455</v>
+        <v>0.1715221822588789</v>
       </c>
       <c r="E176">
-        <v>0.1753985931109907</v>
+        <v>0.1036751811064769</v>
       </c>
     </row>
     <row r="177">
@@ -4031,10 +4031,10 @@
         </is>
       </c>
       <c r="D177">
-        <v>-0.2616084161051431</v>
+        <v>0.1715526620705857</v>
       </c>
       <c r="E177">
-        <v>0.1759605504000444</v>
+        <v>0.1027176199494718</v>
       </c>
     </row>
     <row r="178">
@@ -4052,10 +4052,10 @@
         </is>
       </c>
       <c r="D178">
-        <v>-0.2636857030485499</v>
+        <v>0.2185214130076223</v>
       </c>
       <c r="E178">
-        <v>0.1738051757834869</v>
+        <v>0.08398745578541643</v>
       </c>
     </row>
     <row r="179">
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="D179">
-        <v>-0.2636857030485499</v>
+        <v>0.1576896809062693</v>
       </c>
       <c r="E179">
-        <v>0.1738051757834869</v>
+        <v>0.1120948106396098</v>
       </c>
     </row>
     <row r="180">
@@ -4094,10 +4094,10 @@
         </is>
       </c>
       <c r="D180">
-        <v>-0.2463422007738622</v>
+        <v>0.1361447220708623</v>
       </c>
       <c r="E180">
-        <v>0.1595078824472851</v>
+        <v>0.09701290577468469</v>
       </c>
     </row>
     <row r="181">
@@ -4115,10 +4115,10 @@
         </is>
       </c>
       <c r="D181">
-        <v>-0.2489197989812178</v>
+        <v>0.1721244752054119</v>
       </c>
       <c r="E181">
-        <v>0.1637262055937909</v>
+        <v>0.1016531798131691</v>
       </c>
     </row>
     <row r="182">
@@ -4136,10 +4136,10 @@
         </is>
       </c>
       <c r="D182">
-        <v>-0.2800636495164435</v>
+        <v>0.1715257293316203</v>
       </c>
       <c r="E182">
-        <v>0.175248570397873</v>
+        <v>0.1035656042661377</v>
       </c>
     </row>
     <row r="183">
@@ -4157,10 +4157,10 @@
         </is>
       </c>
       <c r="D183">
-        <v>-0.2800636495164435</v>
+        <v>0.169104965796146</v>
       </c>
       <c r="E183">
-        <v>0.175248570397873</v>
+        <v>0.1024697640501593</v>
       </c>
     </row>
     <row r="184">
@@ -4178,10 +4178,10 @@
         </is>
       </c>
       <c r="D184">
-        <v>-0.2796307887700967</v>
+        <v>0.1701239472611172</v>
       </c>
       <c r="E184">
-        <v>0.173767279162987</v>
+        <v>0.1019551190048387</v>
       </c>
     </row>
     <row r="185">
@@ -4194,10 +4194,10 @@
         <v>37</v>
       </c>
       <c r="D185">
-        <v>-0.2800636495164435</v>
+        <v>0.1715257293316204</v>
       </c>
       <c r="E185">
-        <v>0.175248570397873</v>
+        <v>0.1035656042661377</v>
       </c>
     </row>
     <row r="186">
@@ -4210,10 +4210,10 @@
         <v>39</v>
       </c>
       <c r="D186">
-        <v>-0.2796574726261621</v>
+        <v>0.1715541873967248</v>
       </c>
       <c r="E186">
-        <v>0.1738593017045983</v>
+        <v>0.1026687221080961</v>
       </c>
     </row>
     <row r="187">
@@ -4223,18 +4223,18 @@
         </is>
       </c>
       <c r="B187">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Sibanda M.</t>
+          <t>Gonçalves M.C.</t>
         </is>
       </c>
       <c r="D187">
-        <v>0.1805237721631213</v>
+        <v>0</v>
       </c>
       <c r="E187">
-        <v>0.1172603097030837</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="188">
@@ -4244,18 +4244,18 @@
         </is>
       </c>
       <c r="B188">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Frascaroli, F; Bhagwat, S; Guarino, R; Chiarucci,</t>
+          <t>Calvet-Mir L.</t>
         </is>
       </c>
       <c r="D188">
-        <v>0.1098987150981599</v>
+        <v>0</v>
       </c>
       <c r="E188">
-        <v>0.05895552165088383</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="189">
@@ -4265,18 +4265,18 @@
         </is>
       </c>
       <c r="B189">
-        <v>47</v>
+        <v>3</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Rodríguez-Cruz, L.A.; Álvarez-Berríos, N.; Niles, M.T.</t>
+          <t>Bastos J.G.</t>
         </is>
       </c>
       <c r="D189">
-        <v>0.1587417288265827</v>
+        <v>0</v>
       </c>
       <c r="E189">
-        <v>0.1152312670517498</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="190">
@@ -4286,18 +4286,18 @@
         </is>
       </c>
       <c r="B190">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Calvet-Mir L.</t>
+          <t>Romero-Silva M.J.</t>
         </is>
       </c>
       <c r="D190">
-        <v>0.1719167514163476</v>
+        <v>0</v>
       </c>
       <c r="E190">
-        <v>0.101455331262684</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="191">
@@ -4307,18 +4307,18 @@
         </is>
       </c>
       <c r="B191">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Bastos J.G.</t>
+          <t>de Sousa T.B.</t>
         </is>
       </c>
       <c r="D191">
-        <v>0.1715541873910563</v>
+        <v>0</v>
       </c>
       <c r="E191">
-        <v>0.1026687219327556</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="192">
@@ -4328,18 +4328,18 @@
         </is>
       </c>
       <c r="B192">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Romero-Silva M.J.</t>
+          <t>Sarmiento F.O.</t>
         </is>
       </c>
       <c r="D192">
-        <v>0.1715541873910563</v>
+        <v>0</v>
       </c>
       <c r="E192">
-        <v>0.1026687219327556</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="193">
@@ -4349,18 +4349,18 @@
         </is>
       </c>
       <c r="B193">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>de Sousa T.B.</t>
+          <t>Aldasoro Maya E.M.</t>
         </is>
       </c>
       <c r="D193">
-        <v>0.1715541873910563</v>
+        <v>0</v>
       </c>
       <c r="E193">
-        <v>0.1026687219327556</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="194">
@@ -4370,18 +4370,18 @@
         </is>
       </c>
       <c r="B194">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Sarmiento F.O.</t>
+          <t>Franco-Moraes J.</t>
         </is>
       </c>
       <c r="D194">
-        <v>0.1715541873910563</v>
+        <v>0</v>
       </c>
       <c r="E194">
-        <v>0.1026687219327556</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="195">
@@ -4391,18 +4391,18 @@
         </is>
       </c>
       <c r="B195">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Aldasoro Maya E.M.</t>
+          <t>Latorre E.C.</t>
         </is>
       </c>
       <c r="D195">
-        <v>0.1829001275211319</v>
+        <v>0</v>
       </c>
       <c r="E195">
-        <v>0.1042322967106526</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="196">
@@ -4412,18 +4412,18 @@
         </is>
       </c>
       <c r="B196">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Franco-Moraes J.</t>
+          <t>Mobarak C.</t>
         </is>
       </c>
       <c r="D196">
-        <v>0.1790544092277229</v>
+        <v>0</v>
       </c>
       <c r="E196">
-        <v>0.1036031146280961</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="197">
@@ -4433,18 +4433,18 @@
         </is>
       </c>
       <c r="B197">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Latorre E.C.</t>
+          <t>Andreotti F.</t>
         </is>
       </c>
       <c r="D197">
-        <v>0.1715541874001326</v>
+        <v>0</v>
       </c>
       <c r="E197">
-        <v>0.102668722213511</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="198">
@@ -4454,18 +4454,18 @@
         </is>
       </c>
       <c r="B198">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Mobarak C.</t>
+          <t>Suwardi A.B.</t>
         </is>
       </c>
       <c r="D198">
-        <v>0.1715541874001326</v>
+        <v>0</v>
       </c>
       <c r="E198">
-        <v>0.102668722213511</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="199">
@@ -4475,18 +4475,18 @@
         </is>
       </c>
       <c r="B199">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Andreotti F.</t>
+          <t>Plieninger T.</t>
         </is>
       </c>
       <c r="D199">
-        <v>0.1790544092292201</v>
+        <v>0</v>
       </c>
       <c r="E199">
-        <v>0.1036031146519171</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="200">
@@ -4496,18 +4496,18 @@
         </is>
       </c>
       <c r="B200">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Suwardi A.B.</t>
+          <t>Oloriz C.</t>
         </is>
       </c>
       <c r="D200">
-        <v>0.1715541874001326</v>
+        <v>0</v>
       </c>
       <c r="E200">
-        <v>0.102668722213511</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="201">
@@ -4517,18 +4517,18 @@
         </is>
       </c>
       <c r="B201">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Plieninger T.</t>
+          <t>Tran T.A.</t>
         </is>
       </c>
       <c r="D201">
-        <v>0.1715257293299964</v>
+        <v>0</v>
       </c>
       <c r="E201">
-        <v>0.1035656042144892</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="202">
@@ -4538,18 +4538,18 @@
         </is>
       </c>
       <c r="B202">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Oloriz C.</t>
+          <t>Saiba Y.</t>
         </is>
       </c>
       <c r="D202">
-        <v>0.1691049657960305</v>
+        <v>0</v>
       </c>
       <c r="E202">
-        <v>0.1024697640444356</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="203">
@@ -4559,18 +4559,18 @@
         </is>
       </c>
       <c r="B203">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Tran T.A.</t>
+          <t>Vázquez-Delfin P.</t>
         </is>
       </c>
       <c r="D203">
-        <v>0.1700685989500717</v>
+        <v>0</v>
       </c>
       <c r="E203">
-        <v>0.1019839276363107</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="204">
@@ -4580,18 +4580,18 @@
         </is>
       </c>
       <c r="B204">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Saiba Y.</t>
+          <t>Nord A.</t>
         </is>
       </c>
       <c r="D204">
-        <v>0.171554187394143</v>
+        <v>0</v>
       </c>
       <c r="E204">
-        <v>0.1026687220282354</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="205">
@@ -4601,18 +4601,18 @@
         </is>
       </c>
       <c r="B205">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Vázquez-Delfin P.</t>
+          <t>Rollo M.F.</t>
         </is>
       </c>
       <c r="D205">
-        <v>0.1700685989500717</v>
+        <v>0</v>
       </c>
       <c r="E205">
-        <v>0.1019839276363107</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="206">
@@ -4622,18 +4622,18 @@
         </is>
       </c>
       <c r="B206">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Nord A.</t>
+          <t>Sibanda M.</t>
         </is>
       </c>
       <c r="D206">
-        <v>0.1829001275303344</v>
+        <v>0</v>
       </c>
       <c r="E206">
-        <v>0.1042322968436479</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="207">
@@ -4651,10 +4651,10 @@
         </is>
       </c>
       <c r="D207">
-        <v>0.2292775645298313</v>
+        <v>0</v>
       </c>
       <c r="E207">
-        <v>0.06667755147540262</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="208">
@@ -4672,10 +4672,10 @@
         </is>
       </c>
       <c r="D208">
-        <v>0.1576896809062693</v>
+        <v>0</v>
       </c>
       <c r="E208">
-        <v>0.1120948106396098</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="209">
@@ -4685,18 +4685,18 @@
         </is>
       </c>
       <c r="B209">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Alemayehu A.</t>
+          <t>Møller V.</t>
         </is>
       </c>
       <c r="D209">
-        <v>0.1715541873930755</v>
+        <v>0</v>
       </c>
       <c r="E209">
-        <v>0.102668721995211</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="210">
@@ -4706,18 +4706,18 @@
         </is>
       </c>
       <c r="B210">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>La Rosa A.</t>
+          <t>Whaley O.Q.</t>
         </is>
       </c>
       <c r="D210">
-        <v>0.1715257293300479</v>
+        <v>0</v>
       </c>
       <c r="E210">
-        <v>0.1035656042161268</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="211">
@@ -4727,18 +4727,18 @@
         </is>
       </c>
       <c r="B211">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Fernández-Llamazares, A; Cabeza, M</t>
+          <t>Alemayehu A.</t>
         </is>
       </c>
       <c r="D211">
-        <v>0.1790544092292201</v>
+        <v>0</v>
       </c>
       <c r="E211">
-        <v>0.1036031146519171</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="212">
@@ -4748,18 +4748,18 @@
         </is>
       </c>
       <c r="B212">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Gerner, IR; Zerbe, S; Säumel, I</t>
+          <t>Zeleke E.B.</t>
         </is>
       </c>
       <c r="D212">
-        <v>0.1721244752054119</v>
+        <v>0</v>
       </c>
       <c r="E212">
-        <v>0.1016531798131691</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="213">
@@ -4769,18 +4769,18 @@
         </is>
       </c>
       <c r="B213">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Edo, K; Kidane, L; Beyene, T</t>
+          <t>La Rosa A.</t>
         </is>
       </c>
       <c r="D213">
-        <v>0.1715221822588789</v>
+        <v>0</v>
       </c>
       <c r="E213">
-        <v>0.1036751811064769</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="214">
@@ -4790,18 +4790,18 @@
         </is>
       </c>
       <c r="B214">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Mondal, MSH</t>
+          <t>Montoya-Greenheck, F</t>
         </is>
       </c>
       <c r="D214">
-        <v>0.1715526620705857</v>
+        <v>0</v>
       </c>
       <c r="E214">
-        <v>0.1027176199494718</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="215">
@@ -4811,18 +4811,18 @@
         </is>
       </c>
       <c r="B215">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>García, RM; Parra-Quijano, M; Martínez-Fernández,</t>
+          <t>Fernández-Llamazares, A; Cabeza, M</t>
         </is>
       </c>
       <c r="D215">
-        <v>0.2185214130076223</v>
+        <v>0</v>
       </c>
       <c r="E215">
-        <v>0.08398745578541643</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="216">
@@ -4832,18 +4832,18 @@
         </is>
       </c>
       <c r="B216">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Mugi-Ngenga, EW; Mucheru-Muna, MW; Mugwe, JN; Nget</t>
+          <t>Gerner, IR; Zerbe, S; Säumel, I</t>
         </is>
       </c>
       <c r="D216">
-        <v>0.1576896809062693</v>
+        <v>0</v>
       </c>
       <c r="E216">
-        <v>0.1120948106396098</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="217">
@@ -4853,18 +4853,18 @@
         </is>
       </c>
       <c r="B217">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Aswani, S.; Ferse, S.C.A.; Stäbler, M.</t>
+          <t>Frascaroli, F; Bhagwat, S; Guarino, R; Chiarucci,</t>
         </is>
       </c>
       <c r="D217">
-        <v>0.1361447220708623</v>
+        <v>0</v>
       </c>
       <c r="E217">
-        <v>0.09701290577468469</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="218">
@@ -4874,18 +4874,18 @@
         </is>
       </c>
       <c r="B218">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Bussmann, R.W.; Paniagua-Zambrana, N.Y.</t>
+          <t>Edo, K; Kidane, L; Beyene, T</t>
         </is>
       </c>
       <c r="D218">
-        <v>0.1721244752054119</v>
+        <v>0</v>
       </c>
       <c r="E218">
-        <v>0.1016531798131691</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="219">
@@ -4895,18 +4895,18 @@
         </is>
       </c>
       <c r="B219">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Ghanimi, R.; Ouhammou, A.; Babahmad, R.A.</t>
+          <t>Essien, EO; Lamichhane, S; Kalkat, A</t>
         </is>
       </c>
       <c r="D219">
-        <v>0.1715257293316203</v>
+        <v>0</v>
       </c>
       <c r="E219">
-        <v>0.1035656042661377</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="220">
@@ -4916,18 +4916,18 @@
         </is>
       </c>
       <c r="B220">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Malapane, O.L.; Chanza, N.; Musakwa, W.</t>
+          <t>Haghverdi, NP; Davtalab, J; Ghasemi, M; Norouzi, M</t>
         </is>
       </c>
       <c r="D220">
-        <v>0.169104965796146</v>
+        <v>0</v>
       </c>
       <c r="E220">
-        <v>0.1024697640501593</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="221">
@@ -4937,18 +4937,18 @@
         </is>
       </c>
       <c r="B221">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Rodríguez, J.P.; Ørting, B.; Andreasen, C.</t>
+          <t>Mondal, MSH</t>
         </is>
       </c>
       <c r="D221">
-        <v>0.1701239472611172</v>
+        <v>0</v>
       </c>
       <c r="E221">
-        <v>0.1019551190048387</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="222">
@@ -4960,11 +4960,16 @@
       <c r="B222">
         <v>37</v>
       </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Arce, A; de Haan, S; Burra, DD; Ccanto, R</t>
+        </is>
+      </c>
       <c r="D222">
-        <v>0.1715257293316204</v>
+        <v>0</v>
       </c>
       <c r="E222">
-        <v>0.1035656042661377</v>
+        <v>3.076005635424196E-09</v>
       </c>
     </row>
     <row r="223">
@@ -4974,13 +4979,2202 @@
         </is>
       </c>
       <c r="B223">
+        <v>38</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>García, RM; Parra-Quijano, M; Martínez-Fernández,</t>
+        </is>
+      </c>
+      <c r="D223">
+        <v>0</v>
+      </c>
+      <c r="E223">
+        <v>3.076005635424196E-09</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>V6</t>
+        </is>
+      </c>
+      <c r="B224">
         <v>39</v>
       </c>
-      <c r="D223">
-        <v>0.1715541873967248</v>
-      </c>
-      <c r="E223">
-        <v>0.1026687221080961</v>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Loos, J; von Wehrden, H</t>
+        </is>
+      </c>
+      <c r="D224">
+        <v>0</v>
+      </c>
+      <c r="E224">
+        <v>3.076005635424196E-09</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>V6</t>
+        </is>
+      </c>
+      <c r="B225">
+        <v>40</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Avila, JVD; Clement, CR; Junqueira, AB; Ticktin, T</t>
+        </is>
+      </c>
+      <c r="D225">
+        <v>0</v>
+      </c>
+      <c r="E225">
+        <v>3.076005635424196E-09</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>V6</t>
+        </is>
+      </c>
+      <c r="B226">
+        <v>41</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Mugi-Ngenga, EW; Mucheru-Muna, MW; Mugwe, JN; Nget</t>
+        </is>
+      </c>
+      <c r="D226">
+        <v>0</v>
+      </c>
+      <c r="E226">
+        <v>3.076005635424196E-09</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>V6</t>
+        </is>
+      </c>
+      <c r="B227">
+        <v>42</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Cantor, M; Santos-Silva, B; Daura-Jorge, FG; Macha</t>
+        </is>
+      </c>
+      <c r="D227">
+        <v>0</v>
+      </c>
+      <c r="E227">
+        <v>3.076005635424196E-09</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>V6</t>
+        </is>
+      </c>
+      <c r="B228">
+        <v>43</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Aswani, S.; Ferse, S.C.A.; Stäbler, M.</t>
+        </is>
+      </c>
+      <c r="D228">
+        <v>0</v>
+      </c>
+      <c r="E228">
+        <v>3.076005635424196E-09</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>V6</t>
+        </is>
+      </c>
+      <c r="B229">
+        <v>44</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Bussmann, R.W.; Paniagua-Zambrana, N.Y.</t>
+        </is>
+      </c>
+      <c r="D229">
+        <v>0</v>
+      </c>
+      <c r="E229">
+        <v>3.076005635424196E-09</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>V6</t>
+        </is>
+      </c>
+      <c r="B230">
+        <v>45</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Ghanimi, R.; Ouhammou, A.; Babahmad, R.A.</t>
+        </is>
+      </c>
+      <c r="D230">
+        <v>0</v>
+      </c>
+      <c r="E230">
+        <v>3.076005635424196E-09</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>V6</t>
+        </is>
+      </c>
+      <c r="B231">
+        <v>46</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Malapane, O.L.; Chanza, N.; Musakwa, W.</t>
+        </is>
+      </c>
+      <c r="D231">
+        <v>0</v>
+      </c>
+      <c r="E231">
+        <v>3.076005635424196E-09</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>V6</t>
+        </is>
+      </c>
+      <c r="B232">
+        <v>47</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Rodríguez-Cruz, L.A.; Álvarez-Berríos, N.; Niles, M.T.</t>
+        </is>
+      </c>
+      <c r="D232">
+        <v>0</v>
+      </c>
+      <c r="E232">
+        <v>3.076005635424196E-09</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>V6</t>
+        </is>
+      </c>
+      <c r="B233">
+        <v>48</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Rodríguez, J.P.; Ørting, B.; Andreasen, C.</t>
+        </is>
+      </c>
+      <c r="D233">
+        <v>0</v>
+      </c>
+      <c r="E233">
+        <v>3.076005635424196E-09</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B234">
+        <v>1</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Gonçalves M.C.</t>
+        </is>
+      </c>
+      <c r="D234">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E234">
+        <v>2.10745051672371E-09</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B235">
+        <v>2</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Calvet-Mir L.</t>
+        </is>
+      </c>
+      <c r="D235">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E235">
+        <v>2.10745051672371E-09</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B236">
+        <v>3</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Bastos J.G.</t>
+        </is>
+      </c>
+      <c r="D236">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E236">
+        <v>2.10745051672371E-09</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B237">
+        <v>4</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Romero-Silva M.J.</t>
+        </is>
+      </c>
+      <c r="D237">
+        <v>0.02978679932136762</v>
+      </c>
+      <c r="E237">
+        <v>2.535861381655989E-09</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B238">
+        <v>5</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>de Sousa T.B.</t>
+        </is>
+      </c>
+      <c r="D238">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E238">
+        <v>2.10745051672371E-09</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B239">
+        <v>6</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Sarmiento F.O.</t>
+        </is>
+      </c>
+      <c r="D239">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E239">
+        <v>2.10745051672371E-09</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B240">
+        <v>7</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Aldasoro Maya E.M.</t>
+        </is>
+      </c>
+      <c r="D240">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E240">
+        <v>2.10745051672371E-09</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B241">
+        <v>8</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Franco-Moraes J.</t>
+        </is>
+      </c>
+      <c r="D241">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E241">
+        <v>2.10745051672371E-09</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B242">
+        <v>9</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Latorre E.C.</t>
+        </is>
+      </c>
+      <c r="D242">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E242">
+        <v>2.10745051672371E-09</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B243">
+        <v>10</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Mobarak C.</t>
+        </is>
+      </c>
+      <c r="D243">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E243">
+        <v>2.10745051672371E-09</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B244">
+        <v>11</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Andreotti F.</t>
+        </is>
+      </c>
+      <c r="D244">
+        <v>0.05259083030951774</v>
+      </c>
+      <c r="E244">
+        <v>2.145888906265721E-09</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B245">
+        <v>12</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Suwardi A.B.</t>
+        </is>
+      </c>
+      <c r="D245">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E245">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B246">
+        <v>13</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Plieninger T.</t>
+        </is>
+      </c>
+      <c r="D246">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E246">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B247">
+        <v>14</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Oloriz C.</t>
+        </is>
+      </c>
+      <c r="D247">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E247">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B248">
+        <v>15</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Tran T.A.</t>
+        </is>
+      </c>
+      <c r="D248">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E248">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B249">
+        <v>16</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Saiba Y.</t>
+        </is>
+      </c>
+      <c r="D249">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E249">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B250">
+        <v>17</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Vázquez-Delfin P.</t>
+        </is>
+      </c>
+      <c r="D250">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E250">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B251">
+        <v>18</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Nord A.</t>
+        </is>
+      </c>
+      <c r="D251">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E251">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B252">
+        <v>19</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Rollo M.F.</t>
+        </is>
+      </c>
+      <c r="D252">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E252">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B253">
+        <v>20</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Sibanda M.</t>
+        </is>
+      </c>
+      <c r="D253">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E253">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B254">
+        <v>21</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Tabe-Ojong M.P.</t>
+        </is>
+      </c>
+      <c r="D254">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E254">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B255">
+        <v>22</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Aniah P.</t>
+        </is>
+      </c>
+      <c r="D255">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E255">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B256">
+        <v>23</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Møller V.</t>
+        </is>
+      </c>
+      <c r="D256">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E256">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B257">
+        <v>24</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Whaley O.Q.</t>
+        </is>
+      </c>
+      <c r="D257">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E257">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B258">
+        <v>25</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Alemayehu A.</t>
+        </is>
+      </c>
+      <c r="D258">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E258">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B259">
+        <v>26</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Zeleke E.B.</t>
+        </is>
+      </c>
+      <c r="D259">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E259">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B260">
+        <v>27</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>La Rosa A.</t>
+        </is>
+      </c>
+      <c r="D260">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E260">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B261">
+        <v>28</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Montoya-Greenheck, F</t>
+        </is>
+      </c>
+      <c r="D261">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E261">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B262">
+        <v>29</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Fernández-Llamazares, A; Cabeza, M</t>
+        </is>
+      </c>
+      <c r="D262">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E262">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B263">
+        <v>30</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Gerner, IR; Zerbe, S; Säumel, I</t>
+        </is>
+      </c>
+      <c r="D263">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E263">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B264">
+        <v>31</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Frascaroli, F; Bhagwat, S; Guarino, R; Chiarucci,</t>
+        </is>
+      </c>
+      <c r="D264">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E264">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B265">
+        <v>32</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Edo, K; Kidane, L; Beyene, T</t>
+        </is>
+      </c>
+      <c r="D265">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E265">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B266">
+        <v>33</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Essien, EO; Lamichhane, S; Kalkat, A</t>
+        </is>
+      </c>
+      <c r="D266">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E266">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B267">
+        <v>34</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Haghverdi, NP; Davtalab, J; Ghasemi, M; Norouzi, M</t>
+        </is>
+      </c>
+      <c r="D267">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E267">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B268">
+        <v>35</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Mondal, MSH</t>
+        </is>
+      </c>
+      <c r="D268">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E268">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B269">
+        <v>37</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Arce, A; de Haan, S; Burra, DD; Ccanto, R</t>
+        </is>
+      </c>
+      <c r="D269">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E269">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B270">
+        <v>38</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>García, RM; Parra-Quijano, M; Martínez-Fernández,</t>
+        </is>
+      </c>
+      <c r="D270">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E270">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B271">
+        <v>39</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Loos, J; von Wehrden, H</t>
+        </is>
+      </c>
+      <c r="D271">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E271">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B272">
+        <v>40</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Avila, JVD; Clement, CR; Junqueira, AB; Ticktin, T</t>
+        </is>
+      </c>
+      <c r="D272">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E272">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B273">
+        <v>41</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Mugi-Ngenga, EW; Mucheru-Muna, MW; Mugwe, JN; Nget</t>
+        </is>
+      </c>
+      <c r="D273">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E273">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B274">
+        <v>42</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Cantor, M; Santos-Silva, B; Daura-Jorge, FG; Macha</t>
+        </is>
+      </c>
+      <c r="D274">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E274">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B275">
+        <v>43</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Aswani, S.; Ferse, S.C.A.; Stäbler, M.</t>
+        </is>
+      </c>
+      <c r="D275">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E275">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B276">
+        <v>44</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Bussmann, R.W.; Paniagua-Zambrana, N.Y.</t>
+        </is>
+      </c>
+      <c r="D276">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E276">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B277">
+        <v>45</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Ghanimi, R.; Ouhammou, A.; Babahmad, R.A.</t>
+        </is>
+      </c>
+      <c r="D277">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E277">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B278">
+        <v>46</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Malapane, O.L.; Chanza, N.; Musakwa, W.</t>
+        </is>
+      </c>
+      <c r="D278">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E278">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B279">
+        <v>47</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Rodríguez-Cruz, L.A.; Álvarez-Berríos, N.; Niles, M.T.</t>
+        </is>
+      </c>
+      <c r="D279">
+        <v>0.05202680328378667</v>
+      </c>
+      <c r="E279">
+        <v>2.107450516723717E-09</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B280">
+        <v>48</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Rodríguez, J.P.; Ørting, B.; Andreasen, C.</t>
+        </is>
+      </c>
+      <c r="D280">
+        <v>0.02978679932135731</v>
+      </c>
+      <c r="E280">
+        <v>2.536183243886568E-09</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B281">
+        <v>1</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Gonçalves M.C.</t>
+        </is>
+      </c>
+      <c r="D281">
+        <v>0.2803483808066203</v>
+      </c>
+      <c r="E281">
+        <v>4.651299215464971E-10</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B282">
+        <v>2</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Calvet-Mir L.</t>
+        </is>
+      </c>
+      <c r="D282">
+        <v>0.2803483808066203</v>
+      </c>
+      <c r="E282">
+        <v>4.651299215464971E-10</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B283">
+        <v>3</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Bastos J.G.</t>
+        </is>
+      </c>
+      <c r="D283">
+        <v>0.2803483808066203</v>
+      </c>
+      <c r="E283">
+        <v>4.651299215464971E-10</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B284">
+        <v>4</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Romero-Silva M.J.</t>
+        </is>
+      </c>
+      <c r="D284">
+        <v>0.2803483808066203</v>
+      </c>
+      <c r="E284">
+        <v>4.651299215464971E-10</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B285">
+        <v>5</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>de Sousa T.B.</t>
+        </is>
+      </c>
+      <c r="D285">
+        <v>0.2803483808066203</v>
+      </c>
+      <c r="E285">
+        <v>4.651299215464971E-10</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B286">
+        <v>6</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Sarmiento F.O.</t>
+        </is>
+      </c>
+      <c r="D286">
+        <v>0.2803483808066203</v>
+      </c>
+      <c r="E286">
+        <v>4.651299215464971E-10</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B287">
+        <v>7</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Aldasoro Maya E.M.</t>
+        </is>
+      </c>
+      <c r="D287">
+        <v>0.2803483808066203</v>
+      </c>
+      <c r="E287">
+        <v>4.651299215464971E-10</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B288">
+        <v>8</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Franco-Moraes J.</t>
+        </is>
+      </c>
+      <c r="D288">
+        <v>0.2803483808066203</v>
+      </c>
+      <c r="E288">
+        <v>4.651299215464971E-10</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B289">
+        <v>9</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Latorre E.C.</t>
+        </is>
+      </c>
+      <c r="D289">
+        <v>0.2803483808066203</v>
+      </c>
+      <c r="E289">
+        <v>4.651299215464971E-10</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B290">
+        <v>10</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Mobarak C.</t>
+        </is>
+      </c>
+      <c r="D290">
+        <v>0.2803483808066203</v>
+      </c>
+      <c r="E290">
+        <v>4.651299215464971E-10</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B291">
+        <v>11</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Andreotti F.</t>
+        </is>
+      </c>
+      <c r="D291">
+        <v>0.2803483808066203</v>
+      </c>
+      <c r="E291">
+        <v>4.651299215464971E-10</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B292">
+        <v>12</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Suwardi A.B.</t>
+        </is>
+      </c>
+      <c r="D292">
+        <v>0.2803483808066203</v>
+      </c>
+      <c r="E292">
+        <v>4.651299215464971E-10</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B293">
+        <v>13</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Plieninger T.</t>
+        </is>
+      </c>
+      <c r="D293">
+        <v>0.2803483808066203</v>
+      </c>
+      <c r="E293">
+        <v>4.651299215464971E-10</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B294">
+        <v>14</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Oloriz C.</t>
+        </is>
+      </c>
+      <c r="D294">
+        <v>0.2803483808066203</v>
+      </c>
+      <c r="E294">
+        <v>4.651299215464971E-10</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B295">
+        <v>15</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Tran T.A.</t>
+        </is>
+      </c>
+      <c r="D295">
+        <v>0.280938899158505</v>
+      </c>
+      <c r="E295">
+        <v>4.913863000373536E-10</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B296">
+        <v>16</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Saiba Y.</t>
+        </is>
+      </c>
+      <c r="D296">
+        <v>0.2803483808066203</v>
+      </c>
+      <c r="E296">
+        <v>4.651299215464971E-10</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B297">
+        <v>17</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Vázquez-Delfin P.</t>
+        </is>
+      </c>
+      <c r="D297">
+        <v>0.2803483808066203</v>
+      </c>
+      <c r="E297">
+        <v>4.651299215464971E-10</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B298">
+        <v>18</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Nord A.</t>
+        </is>
+      </c>
+      <c r="D298">
+        <v>0.2803483808066203</v>
+      </c>
+      <c r="E298">
+        <v>4.651299215464971E-10</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B299">
+        <v>19</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Rollo M.F.</t>
+        </is>
+      </c>
+      <c r="D299">
+        <v>0.2803483808066203</v>
+      </c>
+      <c r="E299">
+        <v>4.651299215464971E-10</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B300">
+        <v>20</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Sibanda M.</t>
+        </is>
+      </c>
+      <c r="D300">
+        <v>0.2803483808066203</v>
+      </c>
+      <c r="E300">
+        <v>4.651299215464971E-10</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B301">
+        <v>21</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Tabe-Ojong M.P.</t>
+        </is>
+      </c>
+      <c r="D301">
+        <v>0.2803483808066203</v>
+      </c>
+      <c r="E301">
+        <v>4.651299215464971E-10</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B302">
+        <v>22</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Aniah P.</t>
+        </is>
+      </c>
+      <c r="D302">
+        <v>0.2246159803556473</v>
+      </c>
+      <c r="E302">
+        <v>1.351100859505851E-09</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B303">
+        <v>23</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Møller V.</t>
+        </is>
+      </c>
+      <c r="D303">
+        <v>0.2803483808066088</v>
+      </c>
+      <c r="E303">
+        <v>4.651369994484835E-10</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B304">
+        <v>24</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Whaley O.Q.</t>
+        </is>
+      </c>
+      <c r="D304">
+        <v>0.2803483808066088</v>
+      </c>
+      <c r="E304">
+        <v>4.651369994484835E-10</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B305">
+        <v>25</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Alemayehu A.</t>
+        </is>
+      </c>
+      <c r="D305">
+        <v>0.2945949472159848</v>
+      </c>
+      <c r="E305">
+        <v>4.157183026493563E-10</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B306">
+        <v>26</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Zeleke E.B.</t>
+        </is>
+      </c>
+      <c r="D306">
+        <v>0.2809388991585184</v>
+      </c>
+      <c r="E306">
+        <v>4.913781364744001E-10</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B307">
+        <v>27</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>La Rosa A.</t>
+        </is>
+      </c>
+      <c r="D307">
+        <v>0.2803483808066089</v>
+      </c>
+      <c r="E307">
+        <v>4.651369994484835E-10</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B308">
+        <v>28</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Montoya-Greenheck, F</t>
+        </is>
+      </c>
+      <c r="D308">
+        <v>0.2803483808066089</v>
+      </c>
+      <c r="E308">
+        <v>4.651369994484835E-10</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B309">
+        <v>29</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Fernández-Llamazares, A; Cabeza, M</t>
+        </is>
+      </c>
+      <c r="D309">
+        <v>0.2803483808066089</v>
+      </c>
+      <c r="E309">
+        <v>4.651369994484835E-10</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B310">
+        <v>30</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Gerner, IR; Zerbe, S; Säumel, I</t>
+        </is>
+      </c>
+      <c r="D310">
+        <v>0.2803483808066089</v>
+      </c>
+      <c r="E310">
+        <v>4.651369994484835E-10</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B311">
+        <v>31</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Frascaroli, F; Bhagwat, S; Guarino, R; Chiarucci,</t>
+        </is>
+      </c>
+      <c r="D311">
+        <v>0.2803483808066089</v>
+      </c>
+      <c r="E311">
+        <v>4.651369994484835E-10</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B312">
+        <v>32</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Edo, K; Kidane, L; Beyene, T</t>
+        </is>
+      </c>
+      <c r="D312">
+        <v>0.2803483808066089</v>
+      </c>
+      <c r="E312">
+        <v>4.651369994484835E-10</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B313">
+        <v>33</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Essien, EO; Lamichhane, S; Kalkat, A</t>
+        </is>
+      </c>
+      <c r="D313">
+        <v>0.2803483808066089</v>
+      </c>
+      <c r="E313">
+        <v>4.651369994484835E-10</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B314">
+        <v>34</v>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Haghverdi, NP; Davtalab, J; Ghasemi, M; Norouzi, M</t>
+        </is>
+      </c>
+      <c r="D314">
+        <v>0.2803483808066089</v>
+      </c>
+      <c r="E314">
+        <v>4.651369994484835E-10</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B315">
+        <v>35</v>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Mondal, MSH</t>
+        </is>
+      </c>
+      <c r="D315">
+        <v>0.3058997538225108</v>
+      </c>
+      <c r="E315">
+        <v>3.93214082318042E-10</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B316">
+        <v>37</v>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Arce, A; de Haan, S; Burra, DD; Ccanto, R</t>
+        </is>
+      </c>
+      <c r="D316">
+        <v>0.2818040854424941</v>
+      </c>
+      <c r="E316">
+        <v>5.105646002210174E-10</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B317">
+        <v>38</v>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>García, RM; Parra-Quijano, M; Martínez-Fernández,</t>
+        </is>
+      </c>
+      <c r="D317">
+        <v>0.2803483808061279</v>
+      </c>
+      <c r="E317">
+        <v>4.654333629547127E-10</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B318">
+        <v>39</v>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Loos, J; von Wehrden, H</t>
+        </is>
+      </c>
+      <c r="D318">
+        <v>0.2803483808061279</v>
+      </c>
+      <c r="E318">
+        <v>4.654333629547127E-10</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B319">
+        <v>40</v>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Avila, JVD; Clement, CR; Junqueira, AB; Ticktin, T</t>
+        </is>
+      </c>
+      <c r="D319">
+        <v>0.2809388991585184</v>
+      </c>
+      <c r="E319">
+        <v>4.913781364744001E-10</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B320">
+        <v>41</v>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Mugi-Ngenga, EW; Mucheru-Muna, MW; Mugwe, JN; Nget</t>
+        </is>
+      </c>
+      <c r="D320">
+        <v>0.2246159803556473</v>
+      </c>
+      <c r="E320">
+        <v>1.351100859505846E-09</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B321">
+        <v>42</v>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Cantor, M; Santos-Silva, B; Daura-Jorge, FG; Macha</t>
+        </is>
+      </c>
+      <c r="D321">
+        <v>0.2803483808061279</v>
+      </c>
+      <c r="E321">
+        <v>4.654333629547127E-10</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B322">
+        <v>43</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Aswani, S.; Ferse, S.C.A.; Stäbler, M.</t>
+        </is>
+      </c>
+      <c r="D322">
+        <v>0.2803483808061279</v>
+      </c>
+      <c r="E322">
+        <v>4.654333629547127E-10</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B323">
+        <v>44</v>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Bussmann, R.W.; Paniagua-Zambrana, N.Y.</t>
+        </is>
+      </c>
+      <c r="D323">
+        <v>0.2803483808061279</v>
+      </c>
+      <c r="E323">
+        <v>4.654333629547127E-10</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B324">
+        <v>45</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Ghanimi, R.; Ouhammou, A.; Babahmad, R.A.</t>
+        </is>
+      </c>
+      <c r="D324">
+        <v>0.2803483808061279</v>
+      </c>
+      <c r="E324">
+        <v>4.654333629547127E-10</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B325">
+        <v>46</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Malapane, O.L.; Chanza, N.; Musakwa, W.</t>
+        </is>
+      </c>
+      <c r="D325">
+        <v>0.2803483808061279</v>
+      </c>
+      <c r="E325">
+        <v>4.654333629547127E-10</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B326">
+        <v>47</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Rodríguez-Cruz, L.A.; Álvarez-Berríos, N.; Niles, M.T.</t>
+        </is>
+      </c>
+      <c r="D326">
+        <v>0.2772877566960753</v>
+      </c>
+      <c r="E326">
+        <v>5.18605201791178E-10</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B327">
+        <v>48</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Rodríguez, J.P.; Ørting, B.; Andreasen, C.</t>
+        </is>
+      </c>
+      <c r="D327">
+        <v>0.2803483808061279</v>
+      </c>
+      <c r="E327">
+        <v>4.654333629547127E-10</v>
       </c>
     </row>
   </sheetData>
